--- a/data/gravel/Merida Scultura 2025.xlsx
+++ b/data/gravel/Merida Scultura 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{430FDF7B-DBD1-284B-AAA6-FF396C5C4643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C335825-59A9-5740-9427-08EE3F9ACB4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3080" yWindow="500" windowWidth="25720" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="104">
   <si>
     <t>brand</t>
   </si>
@@ -269,9 +269,6 @@
     <t>Scultura</t>
   </si>
   <si>
-    <t>https://www.merida-bikes.com/en/bike/5655/scultura-endurance-gr-700</t>
-  </si>
-  <si>
     <t>FRAME SIZE</t>
   </si>
   <si>
@@ -342,6 +339,12 @@
   </si>
   <si>
     <t>a8:j33</t>
+  </si>
+  <si>
+    <t>https://www.merida-bikes.com/en/bikefinder/tag/scultura-endurance-gr-324</t>
+  </si>
+  <si>
+    <t>https://d27bpu3c1nsd28.cloudfront.net/merida-v2/crud-zoom-img/master/bikes/2026/SCULTURA_ENDURANCE_GR_700_hnyblk_MY26.tif?p1</t>
   </si>
 </sst>
 </file>
@@ -764,7 +767,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>78</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:61" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:61" x14ac:dyDescent="0.3">
@@ -772,7 +780,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -786,16 +794,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>71</v>
@@ -840,10 +848,10 @@
     </row>
     <row r="9" spans="1:61" ht="22" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9" s="7">
         <v>28</v>
@@ -900,7 +908,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C10" s="7">
         <v>380</v>
@@ -957,7 +965,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C11" s="7">
         <v>507</v>
@@ -1014,7 +1022,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C12" s="7">
         <v>418</v>
@@ -1071,7 +1079,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C13" s="7">
         <v>70</v>
@@ -1128,7 +1136,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C14" s="7">
         <v>74.5</v>
@@ -1160,7 +1168,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C15" s="7">
         <v>70</v>
@@ -1192,7 +1200,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C16" s="7">
         <v>125</v>
@@ -1249,7 +1257,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C17" s="7">
         <v>380</v>
@@ -1306,7 +1314,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C18" s="7">
         <v>360</v>
@@ -1338,7 +1346,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C19" s="7">
         <v>528</v>
@@ -1370,7 +1378,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C20" s="7">
         <v>990</v>
@@ -1402,7 +1410,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C21" s="7">
         <v>656</v>
@@ -1445,31 +1453,31 @@
     </row>
     <row r="23" spans="1:35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:35" x14ac:dyDescent="0.3">
@@ -1747,7 +1755,7 @@
         <v>27</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">

--- a/data/gravel/Merida Scultura 2025.xlsx
+++ b/data/gravel/Merida Scultura 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C335825-59A9-5740-9427-08EE3F9ACB4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739D771E-294A-864A-99A7-65AF52FB05FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3080" yWindow="500" windowWidth="25720" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="106">
   <si>
     <t>brand</t>
   </si>
@@ -345,6 +345,12 @@
   </si>
   <si>
     <t>https://d27bpu3c1nsd28.cloudfront.net/merida-v2/crud-zoom-img/master/bikes/2026/SCULTURA_ENDURANCE_GR_700_hnyblk_MY26.tif?p1</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Yuanlin, Changhua, Taiwan</t>
   </si>
 </sst>
 </file>
@@ -723,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BI73"/>
+  <dimension ref="A1:BI74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1895,49 +1901,57 @@
         <v>52</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Merida Scultura 2025.xlsx
+++ b/data/gravel/Merida Scultura 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739D771E-294A-864A-99A7-65AF52FB05FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29340F30-1408-0346-B715-F3433962414D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3080" yWindow="500" windowWidth="25720" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -351,6 +351,24 @@
   </si>
   <si>
     <t>Yuanlin, Changhua, Taiwan</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -729,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BI74"/>
+  <dimension ref="A1:BI80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1825,132 +1843,162 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>42</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>43</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>105</v>
       </c>
     </row>
